--- a/output/pdf_financials_xlsx/SLV.xlsx
+++ b/output/pdf_financials_xlsx/SLV.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.709352</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.707602</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.894193</v>
       </c>
     </row>
     <row r="93">
@@ -3012,7 +3012,11 @@
           <t>Share-based payment reserve (note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>2.709352</v>
       </c>

--- a/output/pdf_financials_xlsx/SLV.xlsx
+++ b/output/pdf_financials_xlsx/SLV.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0688</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.131832</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005377</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.838059</v>
+        <v>-1.906859</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.830619</v>
+        <v>-0.9624509999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.029046</v>
+        <v>-1.034423</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.836647</v>
+        <v>-1.905447</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.829491</v>
+        <v>-0.961323</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.027986</v>
+        <v>-1.033363</v>
       </c>
     </row>
     <row r="30">
@@ -982,7 +982,7 @@
         <v>2.454191</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.526932</v>
       </c>
     </row>
     <row r="35">
@@ -1014,7 +1014,7 @@
         <v>2.454191</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.526932</v>
       </c>
     </row>
     <row r="37">
@@ -1206,7 +1206,7 @@
         <v>0.077351</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.57421</v>
+        <v>0.047278</v>
       </c>
     </row>
     <row r="49">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
